--- a/data/dividends_info_20261023.xlsx
+++ b/data/dividends_info_20261023.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39.02500152587891</v>
+        <v>39.46500015258789</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2306213875233745</v>
+        <v>0.2280501701558927</v>
       </c>
       <c r="J2" t="n">
         <v>143</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>56.25</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.244444444444444</v>
+        <v>1.229148359301742</v>
       </c>
       <c r="J3" t="n">
         <v>122</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.699999809265137</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6896551875334813</v>
+        <v>0.6864988738131719</v>
       </c>
       <c r="J4" t="n">
         <v>52</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39.02500152587891</v>
+        <v>39.46500015258789</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2306213875233745</v>
+        <v>0.2280501701558927</v>
       </c>
       <c r="J6" t="n">
         <v>52</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.045000076293945</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I7" t="n">
-        <v>3.765281033120711</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J7" t="n">
         <v>31</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.65999984741211</v>
+        <v>49.15999984741211</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6659283145713371</v>
+        <v>0.6727013853264052</v>
       </c>
       <c r="J8" t="n">
         <v>31</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>27.30999946594238</v>
+        <v>27.64999961853027</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9886488659097569</v>
+        <v>0.9764918760398587</v>
       </c>
       <c r="J9" t="n">
         <v>31</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25.46999931335449</v>
+        <v>25.93000030517578</v>
       </c>
       <c r="I10" t="n">
-        <v>2.316450788793896</v>
+        <v>2.275356702877603</v>
       </c>
       <c r="J10" t="n">
         <v>31</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.30000019073486</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="I11" t="n">
-        <v>2.038834913701272</v>
+        <v>2.046783580070996</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.949999809265137</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I12" t="n">
-        <v>3.36134464556733</v>
+        <v>3.350083869828403</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.599999904632568</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>1.250000021287374</v>
+        <v>1.238938032185073</v>
       </c>
       <c r="J13" t="n">
         <v>17</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.659999847412109</v>
+        <v>7.670000076293945</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7832898328355801</v>
+        <v>0.7822685710974765</v>
       </c>
       <c r="J14" t="n">
         <v>17</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.89999961853027</v>
+        <v>10.73999977111816</v>
       </c>
       <c r="I15" t="n">
-        <v>4.220183633933238</v>
+        <v>4.283054095001237</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.399999618530273</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7142857467236177</v>
+        <v>0.7317073340929389</v>
       </c>
       <c r="J16" t="n">
         <v>-4</v>
@@ -2796,7 +2796,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2830,7 +2830,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2847,7 +2847,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2857,14 +2857,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2932,7 +2932,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2993,14 +2993,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3034,7 +3034,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3044,14 +3044,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3146,14 +3146,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3187,7 +3187,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3197,14 +3197,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3255,7 +3255,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3265,14 +3265,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3289,7 +3289,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3299,14 +3299,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3350,14 +3350,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3367,14 +3367,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3452,14 +3452,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3493,7 +3493,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3527,7 +3527,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3537,14 +3537,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3595,7 +3595,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3612,7 +3612,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3690,14 +3690,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3707,14 +3707,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3741,14 +3741,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3809,14 +3809,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3833,7 +3833,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3867,7 +3867,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3918,7 +3918,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3928,14 +3928,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3952,7 +3952,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3969,7 +3969,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3979,14 +3979,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4013,14 +4013,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4030,14 +4030,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4088,7 +4088,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4105,7 +4105,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4122,7 +4122,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4132,14 +4132,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4156,7 +4156,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4190,7 +4190,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4200,14 +4200,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4234,14 +4234,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4258,7 +4258,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4336,14 +4336,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4370,14 +4370,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4394,7 +4394,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4438,14 +4438,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4540,14 +4540,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4632,7 +4632,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4751,7 +4751,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4785,7 +4785,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4836,7 +4836,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4853,7 +4853,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4863,14 +4863,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4887,7 +4887,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4938,7 +4938,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4955,7 +4955,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4972,7 +4972,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5023,7 +5023,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5091,7 +5091,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5159,7 +5159,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5210,7 +5210,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5261,7 +5261,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5288,14 +5288,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5322,14 +5322,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5339,14 +5339,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5356,14 +5356,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5414,7 +5414,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5448,7 +5448,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5516,7 +5516,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5707,61 +5707,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>